--- a/IDI_Zone_Eng_Log.xlsx
+++ b/IDI_Zone_Eng_Log.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m_ali\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Laptop\Work\Operational Excellence\SOCOTEC_VISITS App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D73A4750-C553-454A-A7FD-7632A94FBCB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06FB9574-975A-43D3-8926-95D13965F3D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="185">
   <si>
     <t>Area/الحى</t>
   </si>
@@ -160,9 +160,6 @@
     <t>abdulkarim dhumran &amp; ali ghfaely</t>
   </si>
   <si>
-    <t>East Jeddah</t>
-  </si>
-  <si>
     <t>Jeddah</t>
   </si>
   <si>
@@ -178,16 +175,7 @@
     <t>Adel Eid</t>
   </si>
   <si>
-    <t>West Jeddah</t>
-  </si>
-  <si>
     <t>Abdullah AL QURASHI</t>
-  </si>
-  <si>
-    <t>South Jeddah</t>
-  </si>
-  <si>
-    <t>Rabigh</t>
   </si>
   <si>
     <t>Nawaf AFIFI</t>
@@ -541,6 +529,60 @@
   </si>
   <si>
     <t>Meshari ALSHARARI</t>
+  </si>
+  <si>
+    <t>رفحاء</t>
+  </si>
+  <si>
+    <t>عرعر</t>
+  </si>
+  <si>
+    <t>سكاكا</t>
+  </si>
+  <si>
+    <t>دومة الجندل</t>
+  </si>
+  <si>
+    <t>طبرجل</t>
+  </si>
+  <si>
+    <t>القريات</t>
+  </si>
+  <si>
+    <t>طريف</t>
+  </si>
+  <si>
+    <t>جدة-شرق</t>
+  </si>
+  <si>
+    <t>جدة-غرب</t>
+  </si>
+  <si>
+    <t>جدة-جنوب</t>
+  </si>
+  <si>
+    <t>رابغ</t>
+  </si>
+  <si>
+    <t>مكة</t>
+  </si>
+  <si>
+    <t>الطائف</t>
+  </si>
+  <si>
+    <t>عسير</t>
+  </si>
+  <si>
+    <t>أبها</t>
+  </si>
+  <si>
+    <t>القنفذة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">جازان </t>
+  </si>
+  <si>
+    <t>نجران</t>
   </si>
 </sst>
 </file>
@@ -1124,13 +1166,13 @@
         <v>15</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>12</v>
@@ -1172,7 +1214,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>12</v>
@@ -1214,7 +1256,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>12</v>
@@ -1256,7 +1298,7 @@
         <v>11</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>12</v>
@@ -1298,7 +1340,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>12</v>
@@ -1340,7 +1382,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>12</v>
@@ -1382,7 +1424,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>12</v>
@@ -1424,7 +1466,7 @@
         <v>11</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>12</v>
@@ -1466,7 +1508,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>12</v>
@@ -1508,7 +1550,7 @@
         <v>11</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>12</v>
@@ -1550,7 +1592,7 @@
         <v>11</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>12</v>
@@ -1576,17 +1618,17 @@
       <c r="Z13" s="3"/>
     </row>
     <row r="14" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>159</v>
+      <c r="A14" s="6" t="s">
+        <v>167</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
@@ -1618,17 +1660,17 @@
       <c r="Z14" s="3"/>
     </row>
     <row r="15" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>162</v>
+      <c r="A15" s="6" t="s">
+        <v>168</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>11</v>
@@ -1660,17 +1702,17 @@
       <c r="Z15" s="3"/>
     </row>
     <row r="16" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
-        <v>163</v>
+      <c r="A16" s="6" t="s">
+        <v>169</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>11</v>
@@ -1702,17 +1744,17 @@
       <c r="Z16" s="3"/>
     </row>
     <row r="17" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="D17" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>11</v>
@@ -1744,17 +1786,17 @@
       <c r="Z17" s="3"/>
     </row>
     <row r="18" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>165</v>
+      <c r="A18" s="6" t="s">
+        <v>171</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>11</v>
@@ -1786,17 +1828,17 @@
       <c r="Z18" s="3"/>
     </row>
     <row r="19" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>11</v>
@@ -1828,17 +1870,17 @@
       <c r="Z19" s="3"/>
     </row>
     <row r="20" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
-        <v>167</v>
+      <c r="A20" s="6" t="s">
+        <v>173</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>11</v>
@@ -1922,7 +1964,7 @@
         <v>30</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>32</v>
@@ -2090,7 +2132,7 @@
         <v>42</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>32</v>
@@ -2165,25 +2207,25 @@
     </row>
     <row r="28" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="C28" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="D28" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="E28" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="F28" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G28" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
@@ -2207,25 +2249,25 @@
     </row>
     <row r="29" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>50</v>
+        <v>175</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>46</v>
-      </c>
       <c r="D29" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E29" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G29" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
@@ -2249,25 +2291,25 @@
     </row>
     <row r="30" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>52</v>
+        <v>176</v>
       </c>
       <c r="B30" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>46</v>
-      </c>
       <c r="D30" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G30" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
@@ -2291,25 +2333,25 @@
     </row>
     <row r="31" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>53</v>
+        <v>177</v>
       </c>
       <c r="B31" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>46</v>
-      </c>
       <c r="D31" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E31" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G31" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
@@ -2333,25 +2375,25 @@
     </row>
     <row r="32" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>55</v>
+        <v>178</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E32" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G32" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
@@ -2375,25 +2417,25 @@
     </row>
     <row r="33" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>57</v>
+        <v>179</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E33" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G33" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
@@ -2417,25 +2459,25 @@
     </row>
     <row r="34" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>59</v>
+        <v>180</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F34" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G34" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -2459,25 +2501,25 @@
     </row>
     <row r="35" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>63</v>
-      </c>
       <c r="E35" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F35" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G35" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
@@ -2501,25 +2543,25 @@
     </row>
     <row r="36" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>64</v>
+        <v>181</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -2543,25 +2585,25 @@
     </row>
     <row r="37" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>66</v>
+        <v>182</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
@@ -2585,25 +2627,25 @@
     </row>
     <row r="38" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>68</v>
+        <v>183</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
@@ -2627,25 +2669,25 @@
     </row>
     <row r="39" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>70</v>
+        <v>184</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -2669,22 +2711,22 @@
     </row>
     <row r="40" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>12</v>
@@ -2711,22 +2753,22 @@
     </row>
     <row r="41" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>12</v>
@@ -2753,22 +2795,22 @@
     </row>
     <row r="42" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G42" s="5" t="s">
         <v>12</v>
@@ -2795,22 +2837,22 @@
     </row>
     <row r="43" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G43" s="5" t="s">
         <v>12</v>
@@ -2837,22 +2879,22 @@
     </row>
     <row r="44" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>12</v>
@@ -2879,22 +2921,22 @@
     </row>
     <row r="45" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>12</v>
@@ -2921,22 +2963,22 @@
     </row>
     <row r="46" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>12</v>
@@ -2963,22 +3005,22 @@
     </row>
     <row r="47" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>12</v>
@@ -3005,7 +3047,7 @@
     </row>
     <row r="48" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>41</v>
@@ -3014,7 +3056,7 @@
         <v>42</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>32</v>
@@ -3047,22 +3089,22 @@
     </row>
     <row r="49" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>12</v>
@@ -3089,22 +3131,22 @@
     </row>
     <row r="50" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>12</v>
@@ -3131,22 +3173,22 @@
     </row>
     <row r="51" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>12</v>
@@ -3173,22 +3215,22 @@
     </row>
     <row r="52" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>12</v>
@@ -3215,22 +3257,22 @@
     </row>
     <row r="53" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>12</v>
@@ -3257,22 +3299,22 @@
     </row>
     <row r="54" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>12</v>
@@ -3299,22 +3341,22 @@
     </row>
     <row r="55" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>12</v>
@@ -3341,22 +3383,22 @@
     </row>
     <row r="56" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G56" s="5" t="s">
         <v>12</v>
@@ -3383,22 +3425,22 @@
     </row>
     <row r="57" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G57" s="5" t="s">
         <v>12</v>
@@ -3425,22 +3467,22 @@
     </row>
     <row r="58" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G58" s="5" t="s">
         <v>12</v>
@@ -3467,22 +3509,22 @@
     </row>
     <row r="59" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G59" s="5" t="s">
         <v>12</v>
@@ -3512,19 +3554,19 @@
         <v>34</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G60" s="5" t="s">
         <v>12</v>
@@ -3551,22 +3593,22 @@
     </row>
     <row r="61" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G61" s="5" t="s">
         <v>12</v>
@@ -3593,22 +3635,22 @@
     </row>
     <row r="62" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G62" s="5" t="s">
         <v>12</v>
@@ -3635,22 +3677,22 @@
     </row>
     <row r="63" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G63" s="5" t="s">
         <v>12</v>
@@ -3677,22 +3719,22 @@
     </row>
     <row r="64" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G64" s="5" t="s">
         <v>12</v>
@@ -3719,22 +3761,22 @@
     </row>
     <row r="65" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G65" s="5" t="s">
         <v>12</v>
@@ -3761,22 +3803,22 @@
     </row>
     <row r="66" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G66" s="5" t="s">
         <v>12</v>
@@ -3803,22 +3845,22 @@
     </row>
     <row r="67" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G67" s="5" t="s">
         <v>12</v>
@@ -3845,22 +3887,22 @@
     </row>
     <row r="68" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G68" s="5" t="s">
         <v>12</v>
@@ -3887,22 +3929,22 @@
     </row>
     <row r="69" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G69" s="5" t="s">
         <v>12</v>
@@ -3929,22 +3971,22 @@
     </row>
     <row r="70" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G70" s="5" t="s">
         <v>12</v>
@@ -3971,22 +4013,22 @@
     </row>
     <row r="71" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G71" s="5" t="s">
         <v>12</v>
@@ -4013,22 +4055,22 @@
     </row>
     <row r="72" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>12</v>
@@ -4055,22 +4097,22 @@
     </row>
     <row r="73" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G73" s="5" t="s">
         <v>12</v>
@@ -4097,22 +4139,22 @@
     </row>
     <row r="74" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G74" s="5" t="s">
         <v>12</v>
@@ -4139,22 +4181,22 @@
     </row>
     <row r="75" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G75" s="5" t="s">
         <v>12</v>
@@ -4181,22 +4223,22 @@
     </row>
     <row r="76" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G76" s="5" t="s">
         <v>12</v>
@@ -4223,22 +4265,22 @@
     </row>
     <row r="77" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G77" s="5" t="s">
         <v>12</v>
@@ -4265,22 +4307,22 @@
     </row>
     <row r="78" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G78" s="5" t="s">
         <v>12</v>
@@ -4307,22 +4349,22 @@
     </row>
     <row r="79" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G79" s="5" t="s">
         <v>12</v>
@@ -4349,22 +4391,22 @@
     </row>
     <row r="80" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G80" s="5" t="s">
         <v>12</v>
@@ -4391,22 +4433,22 @@
     </row>
     <row r="81" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G81" s="5" t="s">
         <v>12</v>
@@ -4433,22 +4475,22 @@
     </row>
     <row r="82" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G82" s="5" t="s">
         <v>12</v>
@@ -4475,22 +4517,22 @@
     </row>
     <row r="83" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G83" s="5" t="s">
         <v>12</v>
@@ -4517,22 +4559,22 @@
     </row>
     <row r="84" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G84" s="5" t="s">
         <v>12</v>
@@ -4559,22 +4601,22 @@
     </row>
     <row r="85" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G85" s="5" t="s">
         <v>12</v>
@@ -4601,22 +4643,22 @@
     </row>
     <row r="86" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G86" s="5" t="s">
         <v>12</v>
@@ -4643,22 +4685,22 @@
     </row>
     <row r="87" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G87" s="5" t="s">
         <v>12</v>
@@ -4685,22 +4727,22 @@
     </row>
     <row r="88" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G88" s="5" t="s">
         <v>12</v>
@@ -4727,22 +4769,22 @@
     </row>
     <row r="89" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G89" s="5" t="s">
         <v>12</v>
@@ -4769,22 +4811,22 @@
     </row>
     <row r="90" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G90" s="5" t="s">
         <v>12</v>
@@ -4811,22 +4853,22 @@
     </row>
     <row r="91" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G91" s="5" t="s">
         <v>12</v>
@@ -4853,22 +4895,22 @@
     </row>
     <row r="92" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G92" s="5" t="s">
         <v>12</v>
@@ -4895,22 +4937,22 @@
     </row>
     <row r="93" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93" s="6" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G93" s="5" t="s">
         <v>12</v>
@@ -4937,22 +4979,22 @@
     </row>
     <row r="94" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A94" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G94" s="5" t="s">
         <v>12</v>
@@ -4979,22 +5021,22 @@
     </row>
     <row r="95" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A95" s="6" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G95" s="5" t="s">
         <v>12</v>
@@ -5021,22 +5063,22 @@
     </row>
     <row r="96" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A96" s="6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C96" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G96" s="5" t="s">
         <v>12</v>
@@ -30318,12 +30360,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/IDI_Zone_Eng_Log.xlsx
+++ b/IDI_Zone_Eng_Log.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Laptop\Work\Operational Excellence\SOCOTEC_VISITS App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06FB9574-975A-43D3-8926-95D13965F3D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6073BAB3-9280-40F2-8387-C02228670DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$100</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="189">
   <si>
     <t>Area/الحى</t>
   </si>
@@ -175,9 +175,6 @@
     <t>Adel Eid</t>
   </si>
   <si>
-    <t>Abdullah AL QURASHI</t>
-  </si>
-  <si>
     <t>Nawaf AFIFI</t>
   </si>
   <si>
@@ -193,22 +190,7 @@
     <t>Abdullah AL QARNI</t>
   </si>
   <si>
-    <t>Asir</t>
-  </si>
-  <si>
-    <t>Asir Province</t>
-  </si>
-  <si>
-    <t>Abdulelah AL QAHTANI</t>
-  </si>
-  <si>
     <t>Ibrahim ABDEL MASSIH</t>
-  </si>
-  <si>
-    <t>Raed HUWAIZI</t>
-  </si>
-  <si>
-    <t>Abha</t>
   </si>
   <si>
     <t>Abdulkareem GHURMULLAH</t>
@@ -223,13 +205,7 @@
     <t>Jazan</t>
   </si>
   <si>
-    <t>Jazan Province</t>
-  </si>
-  <si>
     <t>Najran</t>
-  </si>
-  <si>
-    <t>Najran Province</t>
   </si>
   <si>
     <t>Hamad ALKHUDAYSH</t>
@@ -552,19 +528,7 @@
     <t>طريف</t>
   </si>
   <si>
-    <t>جدة-شرق</t>
-  </si>
-  <si>
-    <t>جدة-غرب</t>
-  </si>
-  <si>
-    <t>جدة-جنوب</t>
-  </si>
-  <si>
     <t>رابغ</t>
-  </si>
-  <si>
-    <t>مكة</t>
   </si>
   <si>
     <t>الطائف</t>
@@ -579,10 +543,58 @@
     <t>القنفذة</t>
   </si>
   <si>
-    <t xml:space="preserve">جازان </t>
+    <t>نجران</t>
   </si>
   <si>
-    <t>نجران</t>
+    <t>جدة شرق</t>
+  </si>
+  <si>
+    <t>Mohaya ALOTEIBI</t>
+  </si>
+  <si>
+    <t>جدة غرب</t>
+  </si>
+  <si>
+    <t>جدة جنوب</t>
+  </si>
+  <si>
+    <t>جدة شمال</t>
+  </si>
+  <si>
+    <t>Mohammed Raja ALSAHAFI</t>
+  </si>
+  <si>
+    <t>مكة شرق</t>
+  </si>
+  <si>
+    <t>مكة غرب</t>
+  </si>
+  <si>
+    <t>Abdullah AL QORASHI</t>
+  </si>
+  <si>
+    <t>Aasir</t>
+  </si>
+  <si>
+    <t>Raed Huwaizi, Abdulelah Dafer ALQAHTANI</t>
+  </si>
+  <si>
+    <t>Raed Huwaizi</t>
+  </si>
+  <si>
+    <t>خميس مشيط</t>
+  </si>
+  <si>
+    <t>Abdulelah Dafer ALQAHTANI</t>
+  </si>
+  <si>
+    <t>جازان</t>
+  </si>
+  <si>
+    <t>الباحة</t>
+  </si>
+  <si>
+    <t>Albaha</t>
   </si>
 </sst>
 </file>
@@ -637,7 +649,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -656,12 +668,80 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="9"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="9"/>
+      </right>
+      <top style="thin">
+        <color theme="9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="9"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="9"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="9"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="9"/>
+      </right>
+      <top style="thin">
+        <color theme="9"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -681,6 +761,25 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -848,8 +947,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:G96" headerRowDxfId="9" dataDxfId="8" totalsRowDxfId="7">
-  <autoFilter ref="A1:G96" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:G100" headerRowDxfId="9" dataDxfId="8" totalsRowDxfId="7">
+  <autoFilter ref="A1:G100" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Area/الحى" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="City" dataDxfId="5"/>
@@ -1064,7 +1163,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z997"/>
+  <dimension ref="A1:Z985"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="30.109375" style="7" customWidth="1"/>
@@ -1166,13 +1265,13 @@
         <v>15</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>12</v>
@@ -1214,7 +1313,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>12</v>
@@ -1256,7 +1355,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>12</v>
@@ -1298,7 +1397,7 @@
         <v>11</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>12</v>
@@ -1340,7 +1439,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>12</v>
@@ -1382,7 +1481,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>12</v>
@@ -1424,7 +1523,7 @@
         <v>11</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>12</v>
@@ -1466,7 +1565,7 @@
         <v>11</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>12</v>
@@ -1508,7 +1607,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>12</v>
@@ -1550,7 +1649,7 @@
         <v>11</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>12</v>
@@ -1592,7 +1691,7 @@
         <v>11</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>12</v>
@@ -1619,16 +1718,16 @@
     </row>
     <row r="14" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
@@ -1661,16 +1760,16 @@
     </row>
     <row r="15" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>11</v>
@@ -1703,16 +1802,16 @@
     </row>
     <row r="16" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>11</v>
@@ -1745,16 +1844,16 @@
     </row>
     <row r="17" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>11</v>
@@ -1787,16 +1886,16 @@
     </row>
     <row r="18" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>11</v>
@@ -1829,16 +1928,16 @@
     </row>
     <row r="19" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>11</v>
@@ -1871,16 +1970,16 @@
     </row>
     <row r="20" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>11</v>
@@ -1964,7 +2063,7 @@
         <v>30</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>32</v>
@@ -2132,7 +2231,7 @@
         <v>42</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>32</v>
@@ -2207,25 +2306,25 @@
     </row>
     <row r="28" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>174</v>
+        <v>64</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
@@ -2249,25 +2348,25 @@
     </row>
     <row r="29" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>175</v>
+        <v>67</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
@@ -2291,25 +2390,25 @@
     </row>
     <row r="30" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>176</v>
+        <v>69</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>47</v>
+        <v>103</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
@@ -2333,25 +2432,25 @@
     </row>
     <row r="31" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>177</v>
+        <v>71</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
@@ -2375,25 +2474,25 @@
     </row>
     <row r="32" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>178</v>
+        <v>73</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
@@ -2417,25 +2516,25 @@
     </row>
     <row r="33" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>179</v>
+        <v>75</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
@@ -2459,25 +2558,25 @@
     </row>
     <row r="34" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -2501,25 +2600,25 @@
     </row>
     <row r="35" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>180</v>
+        <v>79</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
@@ -2543,25 +2642,25 @@
     </row>
     <row r="36" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>181</v>
+        <v>81</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -2584,26 +2683,26 @@
       <c r="Z36" s="3"/>
     </row>
     <row r="37" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A37" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>48</v>
+      <c r="A37" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
@@ -2626,26 +2725,26 @@
       <c r="Z37" s="3"/>
     </row>
     <row r="38" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>48</v>
+      <c r="A38" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
@@ -2668,26 +2767,26 @@
       <c r="Z38" s="3"/>
     </row>
     <row r="39" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>48</v>
+      <c r="A39" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -2710,25 +2809,25 @@
       <c r="Z39" s="3"/>
     </row>
     <row r="40" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A40" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C40" s="5" t="s">
+      <c r="A40" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C40" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D40" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G40" s="5" t="s">
+      <c r="D40" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>12</v>
       </c>
       <c r="H40" s="3"/>
@@ -2752,25 +2851,25 @@
       <c r="Z40" s="3"/>
     </row>
     <row r="41" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A41" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C41" s="5" t="s">
+      <c r="A41" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C41" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D41" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G41" s="5" t="s">
+      <c r="D41" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G41" s="6" t="s">
         <v>12</v>
       </c>
       <c r="H41" s="3"/>
@@ -2794,25 +2893,25 @@
       <c r="Z41" s="3"/>
     </row>
     <row r="42" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A42" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C42" s="5" t="s">
+      <c r="A42" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D42" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G42" s="5" t="s">
+      <c r="D42" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>12</v>
       </c>
       <c r="H42" s="3"/>
@@ -2836,25 +2935,25 @@
       <c r="Z42" s="3"/>
     </row>
     <row r="43" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A43" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C43" s="5" t="s">
+      <c r="A43" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C43" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D43" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G43" s="5" t="s">
+      <c r="D43" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G43" s="6" t="s">
         <v>12</v>
       </c>
       <c r="H43" s="3"/>
@@ -2878,23 +2977,23 @@
       <c r="Z43" s="3"/>
     </row>
     <row r="44" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A44" s="4" t="s">
-        <v>81</v>
+      <c r="A44" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>12</v>
@@ -2920,23 +3019,23 @@
       <c r="Z44" s="3"/>
     </row>
     <row r="45" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A45" s="4" t="s">
-        <v>83</v>
+      <c r="A45" s="6" t="s">
+        <v>106</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>12</v>
@@ -2962,23 +3061,23 @@
       <c r="Z45" s="3"/>
     </row>
     <row r="46" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A46" s="4" t="s">
-        <v>85</v>
+      <c r="A46" s="6" t="s">
+        <v>107</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>12</v>
@@ -3004,23 +3103,23 @@
       <c r="Z46" s="3"/>
     </row>
     <row r="47" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A47" s="4" t="s">
-        <v>87</v>
+      <c r="A47" s="6" t="s">
+        <v>108</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>12</v>
@@ -3046,23 +3145,23 @@
       <c r="Z47" s="3"/>
     </row>
     <row r="48" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A48" s="4" t="s">
-        <v>89</v>
+      <c r="A48" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>12</v>
@@ -3089,24 +3188,24 @@
     </row>
     <row r="49" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C49" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D49" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G49" s="6" t="s">
+      <c r="D49" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G49" s="5" t="s">
         <v>12</v>
       </c>
       <c r="H49" s="3"/>
@@ -3131,24 +3230,24 @@
     </row>
     <row r="50" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C50" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C50" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D50" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="D50" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G50" s="5" t="s">
         <v>12</v>
       </c>
       <c r="H50" s="3"/>
@@ -3173,24 +3272,24 @@
     </row>
     <row r="51" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C51" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C51" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D51" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G51" s="6" t="s">
+      <c r="D51" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G51" s="5" t="s">
         <v>12</v>
       </c>
       <c r="H51" s="3"/>
@@ -3215,24 +3314,24 @@
     </row>
     <row r="52" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C52" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C52" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D52" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G52" s="6" t="s">
+      <c r="D52" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G52" s="5" t="s">
         <v>12</v>
       </c>
       <c r="H52" s="3"/>
@@ -3257,24 +3356,24 @@
     </row>
     <row r="53" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B53" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="F53" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G53" s="6" t="s">
+      <c r="E53" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G53" s="5" t="s">
         <v>12</v>
       </c>
       <c r="H53" s="3"/>
@@ -3299,24 +3398,24 @@
     </row>
     <row r="54" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C54" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C54" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D54" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G54" s="6" t="s">
+      <c r="D54" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G54" s="5" t="s">
         <v>12</v>
       </c>
       <c r="H54" s="3"/>
@@ -3341,24 +3440,24 @@
     </row>
     <row r="55" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C55" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C55" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D55" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="F55" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G55" s="6" t="s">
+      <c r="D55" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G55" s="5" t="s">
         <v>12</v>
       </c>
       <c r="H55" s="3"/>
@@ -3383,22 +3482,22 @@
     </row>
     <row r="56" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G56" s="5" t="s">
         <v>12</v>
@@ -3425,22 +3524,22 @@
     </row>
     <row r="57" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G57" s="5" t="s">
         <v>12</v>
@@ -3467,22 +3566,22 @@
     </row>
     <row r="58" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G58" s="5" t="s">
         <v>12</v>
@@ -3509,22 +3608,22 @@
     </row>
     <row r="59" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G59" s="5" t="s">
         <v>12</v>
@@ -3551,22 +3650,22 @@
     </row>
     <row r="60" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G60" s="5" t="s">
         <v>12</v>
@@ -3593,22 +3692,22 @@
     </row>
     <row r="61" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G61" s="5" t="s">
         <v>12</v>
@@ -3635,22 +3734,22 @@
     </row>
     <row r="62" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G62" s="5" t="s">
         <v>12</v>
@@ -3677,22 +3776,22 @@
     </row>
     <row r="63" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G63" s="5" t="s">
         <v>12</v>
@@ -3719,22 +3818,22 @@
     </row>
     <row r="64" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G64" s="5" t="s">
         <v>12</v>
@@ -3761,22 +3860,22 @@
     </row>
     <row r="65" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G65" s="5" t="s">
         <v>12</v>
@@ -3803,22 +3902,22 @@
     </row>
     <row r="66" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G66" s="5" t="s">
         <v>12</v>
@@ -3845,22 +3944,22 @@
     </row>
     <row r="67" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G67" s="5" t="s">
         <v>12</v>
@@ -3887,22 +3986,22 @@
     </row>
     <row r="68" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G68" s="5" t="s">
         <v>12</v>
@@ -3929,22 +4028,22 @@
     </row>
     <row r="69" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G69" s="5" t="s">
         <v>12</v>
@@ -3971,22 +4070,22 @@
     </row>
     <row r="70" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G70" s="5" t="s">
         <v>12</v>
@@ -4013,22 +4112,22 @@
     </row>
     <row r="71" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G71" s="5" t="s">
         <v>12</v>
@@ -4055,22 +4154,22 @@
     </row>
     <row r="72" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>12</v>
@@ -4097,22 +4196,22 @@
     </row>
     <row r="73" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G73" s="5" t="s">
         <v>12</v>
@@ -4139,22 +4238,22 @@
     </row>
     <row r="74" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G74" s="5" t="s">
         <v>12</v>
@@ -4181,22 +4280,22 @@
     </row>
     <row r="75" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G75" s="5" t="s">
         <v>12</v>
@@ -4223,22 +4322,22 @@
     </row>
     <row r="76" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G76" s="5" t="s">
         <v>12</v>
@@ -4265,22 +4364,22 @@
     </row>
     <row r="77" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G77" s="5" t="s">
         <v>12</v>
@@ -4307,22 +4406,22 @@
     </row>
     <row r="78" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G78" s="5" t="s">
         <v>12</v>
@@ -4349,22 +4448,22 @@
     </row>
     <row r="79" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G79" s="5" t="s">
         <v>12</v>
@@ -4391,22 +4490,22 @@
     </row>
     <row r="80" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G80" s="5" t="s">
         <v>12</v>
@@ -4433,22 +4532,22 @@
     </row>
     <row r="81" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G81" s="5" t="s">
         <v>12</v>
@@ -4475,22 +4574,22 @@
     </row>
     <row r="82" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G82" s="5" t="s">
         <v>12</v>
@@ -4517,22 +4616,22 @@
     </row>
     <row r="83" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G83" s="5" t="s">
         <v>12</v>
@@ -4559,22 +4658,22 @@
     </row>
     <row r="84" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G84" s="5" t="s">
         <v>12</v>
@@ -4600,26 +4699,26 @@
       <c r="Z84" s="3"/>
     </row>
     <row r="85" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A85" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G85" s="5" t="s">
-        <v>12</v>
+      <c r="A85" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B85" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C85" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D85" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="E85" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F85" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="G85" s="16" t="s">
+        <v>48</v>
       </c>
       <c r="H85" s="3"/>
       <c r="I85" s="3"/>
@@ -4642,26 +4741,26 @@
       <c r="Z85" s="3"/>
     </row>
     <row r="86" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A86" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G86" s="5" t="s">
-        <v>12</v>
+      <c r="A86" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B86" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C86" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D86" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E86" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F86" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="G86" s="16" t="s">
+        <v>48</v>
       </c>
       <c r="H86" s="3"/>
       <c r="I86" s="3"/>
@@ -4684,26 +4783,26 @@
       <c r="Z86" s="3"/>
     </row>
     <row r="87" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A87" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G87" s="5" t="s">
-        <v>12</v>
+      <c r="A87" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="B87" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C87" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D87" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E87" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F87" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="G87" s="16" t="s">
+        <v>48</v>
       </c>
       <c r="H87" s="3"/>
       <c r="I87" s="3"/>
@@ -4726,26 +4825,26 @@
       <c r="Z87" s="3"/>
     </row>
     <row r="88" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A88" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F88" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G88" s="5" t="s">
-        <v>12</v>
+      <c r="A88" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B88" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C88" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D88" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="E88" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F88" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="G88" s="16" t="s">
+        <v>48</v>
       </c>
       <c r="H88" s="3"/>
       <c r="I88" s="3"/>
@@ -4768,26 +4867,26 @@
       <c r="Z88" s="3"/>
     </row>
     <row r="89" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A89" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D89" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F89" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G89" s="5" t="s">
-        <v>12</v>
+      <c r="A89" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="B89" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C89" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D89" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="E89" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F89" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="G89" s="16" t="s">
+        <v>48</v>
       </c>
       <c r="H89" s="3"/>
       <c r="I89" s="3"/>
@@ -4810,26 +4909,26 @@
       <c r="Z89" s="3"/>
     </row>
     <row r="90" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A90" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="B90" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E90" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F90" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G90" s="5" t="s">
-        <v>12</v>
+      <c r="A90" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="B90" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C90" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E90" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F90" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="G90" s="16" t="s">
+        <v>48</v>
       </c>
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
@@ -4852,26 +4951,26 @@
       <c r="Z90" s="3"/>
     </row>
     <row r="91" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A91" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="B91" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F91" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G91" s="5" t="s">
-        <v>12</v>
+      <c r="A91" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B91" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C91" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E91" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F91" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="G91" s="16" t="s">
+        <v>48</v>
       </c>
       <c r="H91" s="3"/>
       <c r="I91" s="3"/>
@@ -4894,26 +4993,26 @@
       <c r="Z91" s="3"/>
     </row>
     <row r="92" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A92" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E92" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F92" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G92" s="5" t="s">
-        <v>12</v>
+      <c r="A92" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B92" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C92" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D92" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E92" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F92" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G92" s="17" t="s">
+        <v>48</v>
       </c>
       <c r="H92" s="3"/>
       <c r="I92" s="3"/>
@@ -4936,26 +5035,26 @@
       <c r="Z92" s="3"/>
     </row>
     <row r="93" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A93" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="B93" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D93" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F93" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G93" s="5" t="s">
-        <v>12</v>
+      <c r="A93" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="B93" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C93" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D93" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E93" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F93" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="G93" s="16" t="s">
+        <v>48</v>
       </c>
       <c r="H93" s="3"/>
       <c r="I93" s="3"/>
@@ -4978,26 +5077,26 @@
       <c r="Z93" s="3"/>
     </row>
     <row r="94" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A94" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E94" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F94" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G94" s="5" t="s">
-        <v>12</v>
+      <c r="A94" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B94" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C94" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="E94" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F94" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="G94" s="16" t="s">
+        <v>48</v>
       </c>
       <c r="H94" s="3"/>
       <c r="I94" s="3"/>
@@ -5020,26 +5119,26 @@
       <c r="Z94" s="3"/>
     </row>
     <row r="95" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A95" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B95" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E95" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F95" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G95" s="5" t="s">
-        <v>12</v>
+      <c r="A95" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B95" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="C95" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="D95" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E95" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F95" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="G95" s="16" t="s">
+        <v>48</v>
       </c>
       <c r="H95" s="3"/>
       <c r="I95" s="3"/>
@@ -5062,26 +5161,26 @@
       <c r="Z95" s="3"/>
     </row>
     <row r="96" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A96" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="B96" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C96" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E96" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G96" s="5" t="s">
-        <v>12</v>
+      <c r="A96" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="B96" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="C96" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="D96" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E96" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F96" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="G96" s="16" t="s">
+        <v>48</v>
       </c>
       <c r="H96" s="3"/>
       <c r="I96" s="3"/>
@@ -5104,13 +5203,27 @@
       <c r="Z96" s="3"/>
     </row>
     <row r="97" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A97" s="3"/>
-      <c r="B97" s="3"/>
-      <c r="C97" s="3"/>
-      <c r="D97" s="3"/>
-      <c r="E97" s="3"/>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3"/>
+      <c r="A97" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="B97" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="C97" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="D97" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E97" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F97" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="G97" s="16" t="s">
+        <v>48</v>
+      </c>
       <c r="H97" s="3"/>
       <c r="I97" s="3"/>
       <c r="J97" s="3"/>
@@ -5132,13 +5245,27 @@
       <c r="Z97" s="3"/>
     </row>
     <row r="98" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A98" s="3"/>
-      <c r="B98" s="3"/>
-      <c r="C98" s="3"/>
-      <c r="D98" s="3"/>
-      <c r="E98" s="3"/>
-      <c r="F98" s="3"/>
-      <c r="G98" s="3"/>
+      <c r="A98" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="B98" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C98" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D98" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="E98" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F98" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="G98" s="16" t="s">
+        <v>48</v>
+      </c>
       <c r="H98" s="3"/>
       <c r="I98" s="3"/>
       <c r="J98" s="3"/>
@@ -5160,13 +5287,27 @@
       <c r="Z98" s="3"/>
     </row>
     <row r="99" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A99" s="3"/>
-      <c r="B99" s="3"/>
-      <c r="C99" s="3"/>
-      <c r="D99" s="3"/>
-      <c r="E99" s="3"/>
-      <c r="F99" s="3"/>
-      <c r="G99" s="3"/>
+      <c r="A99" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="B99" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C99" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D99" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E99" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F99" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G99" s="17" t="s">
+        <v>48</v>
+      </c>
       <c r="H99" s="3"/>
       <c r="I99" s="3"/>
       <c r="J99" s="3"/>
@@ -5188,13 +5329,27 @@
       <c r="Z99" s="3"/>
     </row>
     <row r="100" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A100" s="3"/>
-      <c r="B100" s="3"/>
-      <c r="C100" s="3"/>
-      <c r="D100" s="3"/>
-      <c r="E100" s="3"/>
-      <c r="F100" s="3"/>
-      <c r="G100" s="3"/>
+      <c r="A100" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="B100" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="C100" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="D100" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E100" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F100" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G100" s="16" t="s">
+        <v>48</v>
+      </c>
       <c r="H100" s="3"/>
       <c r="I100" s="3"/>
       <c r="J100" s="3"/>
@@ -29995,351 +30150,15 @@
       <c r="Y985" s="3"/>
       <c r="Z985" s="3"/>
     </row>
-    <row r="986" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A986" s="3"/>
-      <c r="B986" s="3"/>
-      <c r="C986" s="3"/>
-      <c r="D986" s="3"/>
-      <c r="E986" s="3"/>
-      <c r="F986" s="3"/>
-      <c r="G986" s="3"/>
-      <c r="H986" s="3"/>
-      <c r="I986" s="3"/>
-      <c r="J986" s="3"/>
-      <c r="K986" s="3"/>
-      <c r="L986" s="3"/>
-      <c r="M986" s="3"/>
-      <c r="N986" s="3"/>
-      <c r="O986" s="3"/>
-      <c r="P986" s="3"/>
-      <c r="Q986" s="3"/>
-      <c r="R986" s="3"/>
-      <c r="S986" s="3"/>
-      <c r="T986" s="3"/>
-      <c r="U986" s="3"/>
-      <c r="V986" s="3"/>
-      <c r="W986" s="3"/>
-      <c r="X986" s="3"/>
-      <c r="Y986" s="3"/>
-      <c r="Z986" s="3"/>
-    </row>
-    <row r="987" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A987" s="3"/>
-      <c r="B987" s="3"/>
-      <c r="C987" s="3"/>
-      <c r="D987" s="3"/>
-      <c r="E987" s="3"/>
-      <c r="F987" s="3"/>
-      <c r="G987" s="3"/>
-      <c r="H987" s="3"/>
-      <c r="I987" s="3"/>
-      <c r="J987" s="3"/>
-      <c r="K987" s="3"/>
-      <c r="L987" s="3"/>
-      <c r="M987" s="3"/>
-      <c r="N987" s="3"/>
-      <c r="O987" s="3"/>
-      <c r="P987" s="3"/>
-      <c r="Q987" s="3"/>
-      <c r="R987" s="3"/>
-      <c r="S987" s="3"/>
-      <c r="T987" s="3"/>
-      <c r="U987" s="3"/>
-      <c r="V987" s="3"/>
-      <c r="W987" s="3"/>
-      <c r="X987" s="3"/>
-      <c r="Y987" s="3"/>
-      <c r="Z987" s="3"/>
-    </row>
-    <row r="988" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A988" s="3"/>
-      <c r="B988" s="3"/>
-      <c r="C988" s="3"/>
-      <c r="D988" s="3"/>
-      <c r="E988" s="3"/>
-      <c r="F988" s="3"/>
-      <c r="G988" s="3"/>
-      <c r="H988" s="3"/>
-      <c r="I988" s="3"/>
-      <c r="J988" s="3"/>
-      <c r="K988" s="3"/>
-      <c r="L988" s="3"/>
-      <c r="M988" s="3"/>
-      <c r="N988" s="3"/>
-      <c r="O988" s="3"/>
-      <c r="P988" s="3"/>
-      <c r="Q988" s="3"/>
-      <c r="R988" s="3"/>
-      <c r="S988" s="3"/>
-      <c r="T988" s="3"/>
-      <c r="U988" s="3"/>
-      <c r="V988" s="3"/>
-      <c r="W988" s="3"/>
-      <c r="X988" s="3"/>
-      <c r="Y988" s="3"/>
-      <c r="Z988" s="3"/>
-    </row>
-    <row r="989" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A989" s="3"/>
-      <c r="B989" s="3"/>
-      <c r="C989" s="3"/>
-      <c r="D989" s="3"/>
-      <c r="E989" s="3"/>
-      <c r="F989" s="3"/>
-      <c r="G989" s="3"/>
-      <c r="H989" s="3"/>
-      <c r="I989" s="3"/>
-      <c r="J989" s="3"/>
-      <c r="K989" s="3"/>
-      <c r="L989" s="3"/>
-      <c r="M989" s="3"/>
-      <c r="N989" s="3"/>
-      <c r="O989" s="3"/>
-      <c r="P989" s="3"/>
-      <c r="Q989" s="3"/>
-      <c r="R989" s="3"/>
-      <c r="S989" s="3"/>
-      <c r="T989" s="3"/>
-      <c r="U989" s="3"/>
-      <c r="V989" s="3"/>
-      <c r="W989" s="3"/>
-      <c r="X989" s="3"/>
-      <c r="Y989" s="3"/>
-      <c r="Z989" s="3"/>
-    </row>
-    <row r="990" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A990" s="3"/>
-      <c r="B990" s="3"/>
-      <c r="C990" s="3"/>
-      <c r="D990" s="3"/>
-      <c r="E990" s="3"/>
-      <c r="F990" s="3"/>
-      <c r="G990" s="3"/>
-      <c r="H990" s="3"/>
-      <c r="I990" s="3"/>
-      <c r="J990" s="3"/>
-      <c r="K990" s="3"/>
-      <c r="L990" s="3"/>
-      <c r="M990" s="3"/>
-      <c r="N990" s="3"/>
-      <c r="O990" s="3"/>
-      <c r="P990" s="3"/>
-      <c r="Q990" s="3"/>
-      <c r="R990" s="3"/>
-      <c r="S990" s="3"/>
-      <c r="T990" s="3"/>
-      <c r="U990" s="3"/>
-      <c r="V990" s="3"/>
-      <c r="W990" s="3"/>
-      <c r="X990" s="3"/>
-      <c r="Y990" s="3"/>
-      <c r="Z990" s="3"/>
-    </row>
-    <row r="991" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A991" s="3"/>
-      <c r="B991" s="3"/>
-      <c r="C991" s="3"/>
-      <c r="D991" s="3"/>
-      <c r="E991" s="3"/>
-      <c r="F991" s="3"/>
-      <c r="G991" s="3"/>
-      <c r="H991" s="3"/>
-      <c r="I991" s="3"/>
-      <c r="J991" s="3"/>
-      <c r="K991" s="3"/>
-      <c r="L991" s="3"/>
-      <c r="M991" s="3"/>
-      <c r="N991" s="3"/>
-      <c r="O991" s="3"/>
-      <c r="P991" s="3"/>
-      <c r="Q991" s="3"/>
-      <c r="R991" s="3"/>
-      <c r="S991" s="3"/>
-      <c r="T991" s="3"/>
-      <c r="U991" s="3"/>
-      <c r="V991" s="3"/>
-      <c r="W991" s="3"/>
-      <c r="X991" s="3"/>
-      <c r="Y991" s="3"/>
-      <c r="Z991" s="3"/>
-    </row>
-    <row r="992" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A992" s="3"/>
-      <c r="B992" s="3"/>
-      <c r="C992" s="3"/>
-      <c r="D992" s="3"/>
-      <c r="E992" s="3"/>
-      <c r="F992" s="3"/>
-      <c r="G992" s="3"/>
-      <c r="H992" s="3"/>
-      <c r="I992" s="3"/>
-      <c r="J992" s="3"/>
-      <c r="K992" s="3"/>
-      <c r="L992" s="3"/>
-      <c r="M992" s="3"/>
-      <c r="N992" s="3"/>
-      <c r="O992" s="3"/>
-      <c r="P992" s="3"/>
-      <c r="Q992" s="3"/>
-      <c r="R992" s="3"/>
-      <c r="S992" s="3"/>
-      <c r="T992" s="3"/>
-      <c r="U992" s="3"/>
-      <c r="V992" s="3"/>
-      <c r="W992" s="3"/>
-      <c r="X992" s="3"/>
-      <c r="Y992" s="3"/>
-      <c r="Z992" s="3"/>
-    </row>
-    <row r="993" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A993" s="3"/>
-      <c r="B993" s="3"/>
-      <c r="C993" s="3"/>
-      <c r="D993" s="3"/>
-      <c r="E993" s="3"/>
-      <c r="F993" s="3"/>
-      <c r="G993" s="3"/>
-      <c r="H993" s="3"/>
-      <c r="I993" s="3"/>
-      <c r="J993" s="3"/>
-      <c r="K993" s="3"/>
-      <c r="L993" s="3"/>
-      <c r="M993" s="3"/>
-      <c r="N993" s="3"/>
-      <c r="O993" s="3"/>
-      <c r="P993" s="3"/>
-      <c r="Q993" s="3"/>
-      <c r="R993" s="3"/>
-      <c r="S993" s="3"/>
-      <c r="T993" s="3"/>
-      <c r="U993" s="3"/>
-      <c r="V993" s="3"/>
-      <c r="W993" s="3"/>
-      <c r="X993" s="3"/>
-      <c r="Y993" s="3"/>
-      <c r="Z993" s="3"/>
-    </row>
-    <row r="994" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A994" s="3"/>
-      <c r="B994" s="3"/>
-      <c r="C994" s="3"/>
-      <c r="D994" s="3"/>
-      <c r="E994" s="3"/>
-      <c r="F994" s="3"/>
-      <c r="G994" s="3"/>
-      <c r="H994" s="3"/>
-      <c r="I994" s="3"/>
-      <c r="J994" s="3"/>
-      <c r="K994" s="3"/>
-      <c r="L994" s="3"/>
-      <c r="M994" s="3"/>
-      <c r="N994" s="3"/>
-      <c r="O994" s="3"/>
-      <c r="P994" s="3"/>
-      <c r="Q994" s="3"/>
-      <c r="R994" s="3"/>
-      <c r="S994" s="3"/>
-      <c r="T994" s="3"/>
-      <c r="U994" s="3"/>
-      <c r="V994" s="3"/>
-      <c r="W994" s="3"/>
-      <c r="X994" s="3"/>
-      <c r="Y994" s="3"/>
-      <c r="Z994" s="3"/>
-    </row>
-    <row r="995" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A995" s="3"/>
-      <c r="B995" s="3"/>
-      <c r="C995" s="3"/>
-      <c r="D995" s="3"/>
-      <c r="E995" s="3"/>
-      <c r="F995" s="3"/>
-      <c r="G995" s="3"/>
-      <c r="H995" s="3"/>
-      <c r="I995" s="3"/>
-      <c r="J995" s="3"/>
-      <c r="K995" s="3"/>
-      <c r="L995" s="3"/>
-      <c r="M995" s="3"/>
-      <c r="N995" s="3"/>
-      <c r="O995" s="3"/>
-      <c r="P995" s="3"/>
-      <c r="Q995" s="3"/>
-      <c r="R995" s="3"/>
-      <c r="S995" s="3"/>
-      <c r="T995" s="3"/>
-      <c r="U995" s="3"/>
-      <c r="V995" s="3"/>
-      <c r="W995" s="3"/>
-      <c r="X995" s="3"/>
-      <c r="Y995" s="3"/>
-      <c r="Z995" s="3"/>
-    </row>
-    <row r="996" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A996" s="3"/>
-      <c r="B996" s="3"/>
-      <c r="C996" s="3"/>
-      <c r="D996" s="3"/>
-      <c r="E996" s="3"/>
-      <c r="F996" s="3"/>
-      <c r="G996" s="3"/>
-      <c r="H996" s="3"/>
-      <c r="I996" s="3"/>
-      <c r="J996" s="3"/>
-      <c r="K996" s="3"/>
-      <c r="L996" s="3"/>
-      <c r="M996" s="3"/>
-      <c r="N996" s="3"/>
-      <c r="O996" s="3"/>
-      <c r="P996" s="3"/>
-      <c r="Q996" s="3"/>
-      <c r="R996" s="3"/>
-      <c r="S996" s="3"/>
-      <c r="T996" s="3"/>
-      <c r="U996" s="3"/>
-      <c r="V996" s="3"/>
-      <c r="W996" s="3"/>
-      <c r="X996" s="3"/>
-      <c r="Y996" s="3"/>
-      <c r="Z996" s="3"/>
-    </row>
-    <row r="997" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A997" s="3"/>
-      <c r="B997" s="3"/>
-      <c r="C997" s="3"/>
-      <c r="D997" s="3"/>
-      <c r="E997" s="3"/>
-      <c r="F997" s="3"/>
-      <c r="G997" s="3"/>
-      <c r="H997" s="3"/>
-      <c r="I997" s="3"/>
-      <c r="J997" s="3"/>
-      <c r="K997" s="3"/>
-      <c r="L997" s="3"/>
-      <c r="M997" s="3"/>
-      <c r="N997" s="3"/>
-      <c r="O997" s="3"/>
-      <c r="P997" s="3"/>
-      <c r="Q997" s="3"/>
-      <c r="R997" s="3"/>
-      <c r="S997" s="3"/>
-      <c r="T997" s="3"/>
-      <c r="U997" s="3"/>
-      <c r="V997" s="3"/>
-      <c r="W997" s="3"/>
-      <c r="X997" s="3"/>
-      <c r="Y997" s="3"/>
-      <c r="Z997" s="3"/>
-    </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="C2:C48 C56:C96" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="C44:C94 C2:C36" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Eastern Province,Al-Qassim Province,Medina Province,Hail Province,Tabuk Province,Mecca Province,Asir Province,Jazan Province,Najran Province"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="G2:G48 G56:G96" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="G44:G100 G2:G36" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Omar Abdulkareem,Adel Eid"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="E2:E48 E56:E96" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="E44:E100 E2:E36" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Noaman Rashed,Wahid Ali,Mahmoud IBRAHIM,Ibrahim ABDEL MASSIH,Osama HASSAN"</formula1>
     </dataValidation>
   </dataValidations>
@@ -30360,12 +30179,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
